--- a/internal_doc/03.开发设计/OM/OM功能规划.xlsx
+++ b/internal_doc/03.开发设计/OM/OM功能规划.xlsx
@@ -114,31 +114,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>启停节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将已有集群纳入OM管理（涉及卸载、监控等）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同步PG集群元数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加删除节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>未经OM安装的集群加入到OM中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>经过OM安装但未经OM增删节点的，需要更新最新的节点信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启停节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>将已有集群纳入OM管理（涉及卸载、监控等）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>更新已有OM集群的变化（涉及卸载、监控等）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>同步PG集群元数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加删除节点</t>
+    <t>更新配置等/经过OM安装但未经OM增删节点的，需要更新最新的节点信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -793,39 +793,39 @@
         <v>2</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="27">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="40.5">
       <c r="A23" s="9"/>
       <c r="B23" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="9"/>
       <c r="B24" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="9"/>
       <c r="B25" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="9"/>
       <c r="B26" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C26" s="3"/>
     </row>
